--- a/MainTop/18.03.2026 Таня Новые ВБ/18.03.2026 Таня Новые ВБ.xlsx
+++ b/MainTop/18.03.2026 Таня Новые ВБ/18.03.2026 Таня Новые ВБ.xlsx
@@ -8,24 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Documents\GitHub\Ozon_upload\MainTop\18.03.2026 Таня Новые ВБ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6EF0A4A-8F0A-4241-8CFC-788EBCFC694F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC12BB1-5E80-4FBA-998E-5F883A3A5FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
   <si>
     <t>Термонаклейка Кот сфинкс арт на красном фоне</t>
   </si>
@@ -267,9 +276,6 @@
     <t>Термонаклейка Кот в ванной с бокалом</t>
   </si>
   <si>
-    <t>Термонаклейка Милый котик лапки</t>
-  </si>
-  <si>
     <t>Термонаклейка Кот розовый в цветах арт</t>
   </si>
   <si>
@@ -295,6 +301,9 @@
   </si>
   <si>
     <t>Артикул</t>
+  </si>
+  <si>
+    <t>Термонаклейка Девушка с подсолнухом Аниме</t>
   </si>
 </sst>
 </file>
@@ -363,13 +372,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -653,556 +663,556 @@
   <dimension ref="A1:B90"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="47.28515625" customWidth="1"/>
+    <col min="1" max="1" width="59.42578125" customWidth="1"/>
     <col min="2" max="2" width="4.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B52" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B53" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B54" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B55" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B56" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B57" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B58" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B59" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B60" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B61" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B62" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B63" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B64" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B65" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B66" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B67" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="B68" s="3">
         <v>4</v>
       </c>
-      <c r="B6" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B32" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B33" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B35" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B47" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B48" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B49" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B50" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B51" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B52" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B53" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B54" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B55" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B56" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B57" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B58" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B59" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B60" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B61" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B62" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B63" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B64" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B65" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B66" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B67" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B68" s="3">
-        <v>2</v>
-      </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
+      <c r="A69" s="4" t="s">
         <v>66</v>
       </c>
       <c r="B69" s="3">
@@ -1210,7 +1220,7 @@
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
+      <c r="A70" s="4" t="s">
         <v>67</v>
       </c>
       <c r="B70" s="3">
@@ -1218,7 +1228,7 @@
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="2" t="s">
+      <c r="A71" s="4" t="s">
         <v>68</v>
       </c>
       <c r="B71" s="3">
@@ -1226,7 +1236,7 @@
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="2" t="s">
+      <c r="A72" s="4" t="s">
         <v>69</v>
       </c>
       <c r="B72" s="3">
@@ -1234,7 +1244,7 @@
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="2" t="s">
+      <c r="A73" s="4" t="s">
         <v>70</v>
       </c>
       <c r="B73" s="3">
@@ -1242,7 +1252,7 @@
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="2" t="s">
+      <c r="A74" s="4" t="s">
         <v>71</v>
       </c>
       <c r="B74" s="3">
@@ -1250,7 +1260,7 @@
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="2" t="s">
+      <c r="A75" s="4" t="s">
         <v>72</v>
       </c>
       <c r="B75" s="3">
@@ -1258,7 +1268,7 @@
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="2" t="s">
+      <c r="A76" s="4" t="s">
         <v>73</v>
       </c>
       <c r="B76" s="3">
@@ -1266,7 +1276,7 @@
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="2" t="s">
+      <c r="A77" s="4" t="s">
         <v>74</v>
       </c>
       <c r="B77" s="3">
@@ -1274,7 +1284,7 @@
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="2" t="s">
+      <c r="A78" s="4" t="s">
         <v>75</v>
       </c>
       <c r="B78" s="3">
@@ -1282,7 +1292,7 @@
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="2" t="s">
+      <c r="A79" s="4" t="s">
         <v>76</v>
       </c>
       <c r="B79" s="3">
@@ -1290,7 +1300,7 @@
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="2" t="s">
+      <c r="A80" s="4" t="s">
         <v>77</v>
       </c>
       <c r="B80" s="3">
@@ -1298,7 +1308,7 @@
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="2" t="s">
+      <c r="A81" s="4" t="s">
         <v>78</v>
       </c>
       <c r="B81" s="3">
@@ -1306,7 +1316,7 @@
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="2" t="s">
+      <c r="A82" s="4" t="s">
         <v>79</v>
       </c>
       <c r="B82" s="3">
@@ -1314,7 +1324,7 @@
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="2" t="s">
+      <c r="A83" s="4" t="s">
         <v>80</v>
       </c>
       <c r="B83" s="3">
@@ -1322,7 +1332,7 @@
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="2" t="s">
+      <c r="A84" s="4" t="s">
         <v>81</v>
       </c>
       <c r="B84" s="3">
@@ -1330,7 +1340,7 @@
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="2" t="s">
+      <c r="A85" s="4" t="s">
         <v>82</v>
       </c>
       <c r="B85" s="3">
@@ -1338,7 +1348,7 @@
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="2" t="s">
+      <c r="A86" s="4" t="s">
         <v>83</v>
       </c>
       <c r="B86" s="3">
@@ -1346,7 +1356,7 @@
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="2" t="s">
+      <c r="A87" s="4" t="s">
         <v>84</v>
       </c>
       <c r="B87" s="3">
@@ -1354,7 +1364,7 @@
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="2" t="s">
+      <c r="A88" s="4" t="s">
         <v>85</v>
       </c>
       <c r="B88" s="3">
@@ -1362,7 +1372,7 @@
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="2" t="s">
+      <c r="A89" s="4" t="s">
         <v>86</v>
       </c>
       <c r="B89" s="3">
@@ -1370,12 +1380,8 @@
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B90" s="3">
-        <v>2</v>
-      </c>
+      <c r="A90" s="2"/>
+      <c r="B90" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
